--- a/data/trans_bre/IQ26A_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ26A_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>240,31%</t>
+          <t>165,7%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 7,0</t>
+          <t>-3,53; 6,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 1,46</t>
+          <t>-8,27; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 3,53</t>
+          <t>-5,18; 3,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 26,97</t>
+          <t>-6,4; 25,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-54,37; 265,43</t>
+          <t>-60,42; 248,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,95; 54,68</t>
+          <t>-83,02; 40,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-80,27; 168,22</t>
+          <t>-79,24; 151,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,49</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 1,39</t>
+          <t>-7,75; 1,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 1,03</t>
+          <t>-6,94; 1,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 5,03</t>
+          <t>-5,41; 5,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 30,09</t>
+          <t>-9,87; 22,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,72; 11,99</t>
+          <t>-52,5; 12,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,07; 15,93</t>
+          <t>-58,91; 19,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 41,71</t>
+          <t>-30,39; 44,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 241,57</t>
+          <t>-38,77; 171,56</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,06</t>
+          <t>-2,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-17,46%</t>
+          <t>-9,35%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 9,41</t>
+          <t>-3,56; 9,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 9,35</t>
+          <t>-2,5; 9,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 6,9</t>
+          <t>-6,41; 6,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 11,62</t>
+          <t>-19,38; 13,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 123,21</t>
+          <t>-28,58; 130,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 116,77</t>
+          <t>-19,42; 134,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,6; 54,39</t>
+          <t>-33,58; 50,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,31; 78,75</t>
+          <t>-59,46; 83,15</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,41</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 13,07</t>
+          <t>0,71; 13,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 7,39</t>
+          <t>-5,52; 7,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 10,04</t>
+          <t>-6,16; 8,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 23,02</t>
+          <t>-2,18; 23,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 96,19</t>
+          <t>3,51; 94,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 56,53</t>
+          <t>-28,15; 58,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 61,83</t>
+          <t>-26,55; 52,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 214,6</t>
+          <t>-13,63; 204,2</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,51</t>
+          <t>-1,48; 4,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,18</t>
+          <t>-3,18; 2,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,97</t>
+          <t>-2,61; 3,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 14,41</t>
+          <t>-2,84; 13,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 41,51</t>
+          <t>-11,54; 41,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 22,75</t>
+          <t>-25,0; 27,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 23,99</t>
+          <t>-16,69; 27,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 95,36</t>
+          <t>-13,09; 91,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ26A_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ26A_R2-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,26</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,8</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,77%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-46,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-17,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>165,7%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.12188916538757</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-3.26349845197897</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.8025318037563727</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.704886560273713</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.237665103815376</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4650616773842878</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1763463146543564</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.65698702889197</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,53; 6,32</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,27; 1,31</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,18; 3,34</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,4; 25,63</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-60,42; 248,8</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-83,02; 40,24</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-79,24; 151,87</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.527917734122073</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.269436147327298</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.179848412244095</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.399024862771195</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.6041910771823225</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8302170220668147</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.7924064921257251</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.316859276168617</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.308491421905216</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.337751508176007</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>25.62506558214548</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.488012713466483</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.4023692472982476</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.518711779782654</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-3,31</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,94</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,87</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-26,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-30,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-1,14%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,75; 1,25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,94; 1,14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,41; 5,46</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,87; 22,2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-52,5; 12,32</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-58,91; 19,78</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-30,39; 44,85</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-38,77; 171,56</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-3.313281156102589</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.935764236839812</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.1654933766361638</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>5.871479630054477</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2654330913446236</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3074291567593319</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.0113741530452279</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.2738916017186914</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,34</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,1</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>28,14%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-1,52%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-9,35%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.753656336376223</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.94371705363422</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.411391098230848</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-9.873076660947659</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5249562424849314</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5891076531198395</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3038735069363255</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3877159831910834</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,56; 9,39</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,5; 9,34</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,41; 6,13</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-19,38; 13,02</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-28,58; 130,53</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-19,42; 134,32</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-33,58; 50,62</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-59,46; 83,15</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.254552159614671</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.135754061483875</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.455957886373016</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>22.19822324362717</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1231821160145787</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1978278478739474</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4485323199353822</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.715597539453216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +815,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>58,09%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.917626220202187</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.344811188846301</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.2407699424529314</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.102217881614224</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2814042570844219</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3184118777644851</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.01520542200320386</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.09349047856766499</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,71; 13,37</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,52; 7,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,16; 8,64</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,18; 23,09</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3,51; 94,2</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-28,15; 58,03</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-26,55; 52,51</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-13,63; 204,2</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.55555663079166</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.500293372156693</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.408934048317462</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-19.38078296720044</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2857539657276506</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.194164571314767</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3357841930752616</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5945675260187143</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.393507610776384</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>9.339793504588878</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.133718523055482</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>13.02090653522421</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.305274986500286</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.343229369392621</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5062468862687775</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.8315212260746414</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6.595889039818761</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.183424578398878</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.463058868929068</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>9.629931550733211</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.3928483654811337</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.07168056287290188</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.07404226872884243</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.5808893072963693</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7072506302749528</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.516080938778798</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.16040847650722</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.183548904072142</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.03509519931107793</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2814778610955714</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2655200932160428</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1363253458693757</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>13.36664819083943</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.552457364214933</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.644960083739537</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>23.08868362716859</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.9420436322350553</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.580282011456419</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.5251206720775452</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.04197955771542</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,85</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-5,19%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>25,93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,48; 4,56</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,18; 2,49</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 3,55</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 13,85</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-11,54; 41,56</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-25,0; 27,81</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-16,69; 27,58</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-13,09; 91,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.521405061564127</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.5747571972734331</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04942356508404744</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>4.849190175198132</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1256190342268869</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.05189920856895015</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.003402635782513513</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.2592756608485701</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.483251179502405</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.179606397259212</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.611929340832301</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.840517901503463</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.1154058823863851</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2499556037219895</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1668754702910007</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.130877930817925</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.564165250736426</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.485019826728827</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.547064705075733</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>13.8530238253774</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.4155584844073841</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2781159400673775</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.275846228217617</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.9152031828519622</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1113,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
